--- a/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
+++ b/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_01\Excel\Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE61BDE8-7CE4-45EA-B7CD-6892813F0365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCACB111-F948-40E4-BDD5-AE46771A3608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot 1" sheetId="8" r:id="rId1"/>
@@ -34,7 +34,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="53">
   <si>
     <t>ProductionID</t>
   </si>
@@ -186,9 +186,6 @@
     <t>2023</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
     <t>Sep</t>
   </si>
   <si>
@@ -240,9 +237,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +261,14 @@
       <i/>
       <u/>
       <sz val="36"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,7 +301,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -308,63 +313,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="2">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_ * #,##0.0_ ;_ * \-#,##0.0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="35" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+      <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -649,9 +619,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Automobiles</c:v>
                 </c:pt>
@@ -659,6 +629,9 @@
                   <c:v>Electronics</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -666,18 +639,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>165385</c:v>
+                  <c:v>142768</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81876</c:v>
+                  <c:v>679</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62273</c:v>
+                  <c:v>90859</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>178302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1182,16 +1158,16 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Mike Brown</c:v>
+                  <c:v>Jane Smith</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Emily Davis</c:v>
+                  <c:v>Laura Black</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Chris Green</c:v>
+                  <c:v>David White</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>John Doe</c:v>
+                  <c:v>Mike Brown</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Nancy Grey</c:v>
@@ -1200,7 +1176,7 @@
                   <c:v>Andrew Blue</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Jane Smith</c:v>
+                  <c:v>John Doe</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1212,19 +1188,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
@@ -1675,9 +1651,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$11</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$8</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Oct</c:v>
@@ -1686,21 +1662,12 @@
                     <c:v>Nov</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Apr</c:v>
+                    <c:v>Dec</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>2023</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1708,24 +1675,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$11</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>957</c:v>
+                  <c:v>1143</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>637</c:v>
+                  <c:v>1840</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>688</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1081</c:v>
+                  <c:v>959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2276,7 +2237,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:srgbClr val="FFCC99"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2301,7 +2262,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="CCCCFF"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2376,9 +2337,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Automobiles</c:v>
                 </c:pt>
@@ -2386,6 +2347,9 @@
                   <c:v>Electronics</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2393,18 +2357,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>109.17702014813973</c:v>
+                  <c:v>116.07783789987161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>202.91826923076923</c:v>
+                  <c:v>2.2117263843648209</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>52.411845036689805</c:v>
+                  <c:v>82.9945217959296</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>178.306304928782</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2908,9 +2875,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Automobiles</c:v>
                 </c:pt>
@@ -2918,6 +2885,9 @@
                   <c:v>Electronics</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2925,18 +2895,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>165385</c:v>
+                  <c:v>142768</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>81876</c:v>
+                  <c:v>679</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>62273</c:v>
+                  <c:v>90859</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>178302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3607,16 +3580,16 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Mike Brown</c:v>
+                  <c:v>Jane Smith</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Emily Davis</c:v>
+                  <c:v>Laura Black</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Chris Green</c:v>
+                  <c:v>David White</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>John Doe</c:v>
+                  <c:v>Mike Brown</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Nancy Grey</c:v>
@@ -3625,7 +3598,7 @@
                   <c:v>Andrew Blue</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Jane Smith</c:v>
+                  <c:v>John Doe</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3637,19 +3610,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1</c:v>
@@ -4238,9 +4211,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$11</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$8</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Oct</c:v>
@@ -4249,21 +4222,12 @@
                     <c:v>Nov</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>Jan</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>Feb</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>Apr</c:v>
+                    <c:v>Dec</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>2023</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4271,24 +4235,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$11</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>957</c:v>
+                  <c:v>1143</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>637</c:v>
+                  <c:v>1840</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>199</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>688</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1081</c:v>
+                  <c:v>959</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5113,7 +5071,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:srgbClr val="FFCC99"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5138,7 +5096,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="CCCCFF"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5213,9 +5171,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>Automobiles</c:v>
                 </c:pt>
@@ -5223,6 +5181,9 @@
                   <c:v>Electronics</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -5230,18 +5191,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>109.17702014813973</c:v>
+                  <c:v>116.07783789987161</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>202.91826923076923</c:v>
+                  <c:v>2.2117263843648209</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>52.411845036689805</c:v>
+                  <c:v>82.9945217959296</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>178.306304928782</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11347,8 +11311,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="3" name="Region 1">
@@ -11371,7 +11335,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11425,8 +11389,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="4" name="Gender 1">
@@ -11449,7 +11413,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -11503,8 +11467,8 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="5" name="Quarters (ProductionDate) 1">
@@ -11527,7 +11491,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -13360,8 +13324,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A05C44-8E02-4C0B-897E-E209559CB89E}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A05C44-8E02-4C0B-897E-E209559CB89E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13491,9 +13455,9 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13528,12 +13492,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
         <item x="4"/>
-        <item x="5"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13550,12 +13514,15 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i>
       <x v="3"/>
@@ -13571,7 +13538,7 @@
     <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="13">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13608,7 +13575,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE43A99-DA69-49C7-9999-13295477D628}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE43A99-DA69-49C7-9999-13295477D628}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13754,9 +13721,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13791,12 +13758,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
         <item x="4"/>
-        <item x="5"/>
+        <item h="1" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13815,16 +13782,16 @@
   </rowFields>
   <rowItems count="8">
     <i>
-      <x v="7"/>
+      <x v="4"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="6"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="2"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="7"/>
     </i>
     <i>
       <x v="8"/>
@@ -13833,7 +13800,7 @@
       <x/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -13878,8 +13845,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D064263-4D1C-40D7-BF76-F231D23CFDA0}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D064263-4D1C-40D7-BF76-F231D23CFDA0}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14001,9 +13968,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14038,12 +14005,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
+        <item h="1" sd="0" x="0"/>
+        <item h="1" sd="0" x="1"/>
+        <item h="1" sd="0" x="2"/>
+        <item h="1" sd="0" x="3"/>
         <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
+        <item h="1" sd="0" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14061,7 +14028,7 @@
     <field x="13"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="5">
     <i>
       <x v="1"/>
     </i>
@@ -14071,17 +14038,8 @@
     <i r="1">
       <x v="11"/>
     </i>
-    <i>
-      <x v="2"/>
-    </i>
     <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
+      <x v="12"/>
     </i>
     <i t="grand">
       <x/>
@@ -14126,8 +14084,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87307F0E-6F33-40F7-A92A-4E423868BB78}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87307F0E-6F33-40F7-A92A-4E423868BB78}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14257,9 +14215,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14276,12 +14234,12 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0">
       <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
         <item x="4"/>
-        <item x="5"/>
+        <item h="1" x="5"/>
       </items>
     </pivotField>
     <pivotField showAll="0" defaultSubtotal="0">
@@ -14296,12 +14254,15 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i>
       <x v="3"/>
@@ -14445,7 +14406,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7CA715C-EA03-46A2-9A86-E8A7BB272733}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7CA715C-EA03-46A2-9A86-E8A7BB272733}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14605,10 +14566,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="9">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14636,7 +14597,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB47A8B3-FB3A-4602-8C4B-B1BC5295EBCD}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DB47A8B3-FB3A-4602-8C4B-B1BC5295EBCD}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A8:B21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -14910,9 +14871,9 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="3">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1"/>
-        <i x="2" s="1"/>
+        <i x="2"/>
       </items>
     </tabular>
   </data>
@@ -14950,12 +14911,12 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="6">
-        <i x="1" s="1"/>
-        <i x="2" s="1"/>
+        <i x="1"/>
+        <i x="2"/>
+        <i x="3"/>
         <i x="4" s="1"/>
-        <i x="0" s="1" nd="1"/>
-        <i x="5" s="1" nd="1"/>
-        <i x="3" s="1" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="5" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -15297,14 +15258,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC7590B-59C1-4780-B184-059AA2CBDAFA}">
-  <dimension ref="A3:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -15312,36 +15273,44 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="5">
-        <v>165385</v>
+        <v>142768</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="5">
-        <v>81876</v>
+        <v>679</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5">
+        <v>90859</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5">
-        <v>62273</v>
+      <c r="B7" s="5">
+        <v>178302</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="5">
-        <v>309534</v>
+      <c r="B8" s="5">
+        <v>412608</v>
       </c>
     </row>
   </sheetData>
@@ -15353,13 +15322,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52287D6-AC2A-495B-8F15-E05B7FBCCBFF}">
   <dimension ref="A3:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -15367,68 +15336,68 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="9">
-        <v>4</v>
+      <c r="B7" s="13">
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="9">
-        <v>1</v>
+      <c r="B8" s="13">
+        <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="9">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="9">
-        <v>11</v>
+      <c r="B11" s="13">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -15439,14 +15408,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F3A811-0A1A-4FEF-9853-B1FFC57DE7E8}">
-  <dimension ref="A3:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -15454,68 +15423,44 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="9">
-        <v>1594</v>
+      <c r="B4" s="13">
+        <v>3942</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="13">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="9">
-        <v>957</v>
+      <c r="B6" s="13">
+        <v>1840</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="9">
-        <v>637</v>
+      <c r="B7" s="13">
+        <v>959</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="9">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="9">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="9">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1081</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="9">
-        <v>3562</v>
+      <c r="B8" s="13">
+        <v>3942</v>
       </c>
     </row>
   </sheetData>
@@ -15527,51 +15472,59 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31661C08-08AE-40BA-AF39-38EBBD305E22}">
-  <dimension ref="A3:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:B8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="9">
-        <v>109.17702014813973</v>
+      <c r="B4" s="13">
+        <v>116.07783789987161</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="9">
-        <v>202.91826923076923</v>
+      <c r="B5" s="13">
+        <v>2.2117263843648209</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13">
+        <v>82.9945217959296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="9">
-        <v>52.411845036689805</v>
+      <c r="B7" s="13">
+        <v>178.306304928782</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="9">
-        <v>110.73947222367696</v>
+      <c r="B8" s="13">
+        <v>114.04471030444071</v>
       </c>
     </row>
   </sheetData>
@@ -15583,113 +15536,113 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5574C4D0-95C0-4CFE-87E6-C28A87893F6E}">
   <dimension ref="A1:X4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="9"/>
+      <c r="X3" s="9"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="9"/>
+      <c r="X4" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15710,13 +15663,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2058DF73-A084-498C-876D-E8BC45ABA3AC}">
   <dimension ref="A3:B8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
@@ -15724,43 +15677,43 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="7">
         <v>1152805</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="7">
         <v>604575</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="7">
         <v>703282</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="7">
         <v>910416</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="7">
         <v>3371078</v>
       </c>
     </row>
@@ -15773,79 +15726,79 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97225290-4158-4A01-8DC9-60DB3994B68E}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="12"/>
-      <c r="N3" s="12"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -15853,107 +15806,107 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9">
+        <v>3026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="9">
-        <v>3026</v>
+      <c r="B10">
+        <v>4127</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="9">
-        <v>4127</v>
+      <c r="B11">
+        <v>3875</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="9">
-        <v>3875</v>
+      <c r="B12">
+        <v>1528</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="9">
-        <v>1528</v>
+      <c r="B13">
+        <v>1684</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="9">
-        <v>1684</v>
+      <c r="B14">
+        <v>3537</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="9">
-        <v>3537</v>
+      <c r="B15">
+        <v>1536</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="9">
-        <v>1536</v>
+      <c r="B16">
+        <v>2864</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="9">
-        <v>2864</v>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17">
+        <v>2150</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="9">
-        <v>2150</v>
+      <c r="B18">
+        <v>3103</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="9">
-        <v>3103</v>
+      <c r="B19">
+        <v>4803</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="9">
-        <v>4803</v>
+      <c r="B20">
+        <v>2494</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="9">
-        <v>2494</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21">
         <v>34727</v>
       </c>
     </row>
@@ -15976,57 +15929,57 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -16063,7 +16016,7 @@
         <v>54.097087378640779</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -16100,7 +16053,7 @@
         <v>154.65116279069767</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -16137,7 +16090,7 @@
         <v>159.15481171548117</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -16174,7 +16127,7 @@
         <v>37.187363834422655</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -16211,7 +16164,7 @@
         <v>232.29775280898878</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -16248,7 +16201,7 @@
         <v>49.104738154613464</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -16285,7 +16238,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -16322,7 +16275,7 @@
         <v>116.93288590604027</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -16359,7 +16312,7 @@
         <v>470.78181818181821</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -16396,7 +16349,7 @@
         <v>97.171717171717177</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -16433,7 +16386,7 @@
         <v>94.670040485829958</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -16470,7 +16423,7 @@
         <v>56.590909090909093</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -16507,7 +16460,7 @@
         <v>147.33333333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -16544,7 +16497,7 @@
         <v>2.0451807228915664</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -16581,7 +16534,7 @@
         <v>101.8485639686684</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -16618,7 +16571,7 @@
         <v>97.388601036269435</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -16655,7 +16608,7 @@
         <v>271.05</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -16692,7 +16645,7 @@
         <v>105.32231404958678</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -16729,7 +16682,7 @@
         <v>114.33860045146727</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -16766,7 +16719,7 @@
         <v>81.993957703927492</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -16803,7 +16756,7 @@
         <v>45.54</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -16840,7 +16793,7 @@
         <v>187.13333333333333</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -16877,7 +16830,7 @@
         <v>470.31111111111113</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -16914,7 +16867,7 @@
         <v>93.609170305676855</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -16951,7 +16904,7 @@
         <v>71.50797266514806</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -16988,7 +16941,7 @@
         <v>117.93103448275862</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -17025,7 +16978,7 @@
         <v>31.966824644549764</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -17062,7 +17015,7 @@
         <v>16.378378378378379</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -17099,7 +17052,7 @@
         <v>96.825651302605209</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -17136,7 +17089,7 @@
         <v>52.179310344827584</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -17173,7 +17126,7 @@
         <v>14.21680216802168</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -17210,7 +17163,7 @@
         <v>97.028277634961441</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -17247,7 +17200,7 @@
         <v>1.3287671232876712</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -17284,7 +17237,7 @@
         <v>144.14414414414415</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -17321,7 +17274,7 @@
         <v>133.38461538461539</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -17358,7 +17311,7 @@
         <v>109.29130434782608</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -17395,7 +17348,7 @@
         <v>300.79310344827587</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -17432,7 +17385,7 @@
         <v>122.4</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -17469,7 +17422,7 @@
         <v>51.895161290322584</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -17506,7 +17459,7 @@
         <v>4.1151515151515152</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -17543,7 +17496,7 @@
         <v>691.76470588235293</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -17580,7 +17533,7 @@
         <v>98.141361256544499</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -17617,7 +17570,7 @@
         <v>1.9180790960451977</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -17654,7 +17607,7 @@
         <v>125.18478260869566</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -17691,7 +17644,7 @@
         <v>140.22784810126583</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -17728,7 +17681,7 @@
         <v>138.72294372294371</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -17765,7 +17718,7 @@
         <v>115.56944444444444</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -17802,7 +17755,7 @@
         <v>55.859813084112147</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -17839,7 +17792,7 @@
         <v>496.05405405405406</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -17876,7 +17829,7 @@
         <v>172.88135593220338</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -17913,7 +17866,7 @@
         <v>37.899441340782126</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -17950,7 +17903,7 @@
         <v>97.212827988338191</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -17987,7 +17940,7 @@
         <v>62.857142857142854</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -18024,7 +17977,7 @@
         <v>135.68298368298369</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -18061,7 +18014,7 @@
         <v>121.09572301425662</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -18098,7 +18051,7 @@
         <v>40.325581395348834</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -18135,7 +18088,7 @@
         <v>226.29803921568629</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -18172,7 +18125,7 @@
         <v>370.3</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -18209,7 +18162,7 @@
         <v>91.428571428571431</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -18246,7 +18199,7 @@
         <v>3.8146067415730336</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -18283,7 +18236,7 @@
         <v>56.12582781456954</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -18320,7 +18273,7 @@
         <v>82.859813084112147</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -18357,7 +18310,7 @@
         <v>10.445901639344262</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -18394,7 +18347,7 @@
         <v>3.6117021276595747</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -18431,7 +18384,7 @@
         <v>1.3717171717171717</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -18468,7 +18421,7 @@
         <v>147.63157894736841</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -18505,7 +18458,7 @@
         <v>32.677103718199611</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -18542,7 +18495,7 @@
         <v>90.766233766233768</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -18579,7 +18532,7 @@
         <v>3.7103825136612021</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -18616,7 +18569,7 @@
         <v>110.4</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -18653,7 +18606,7 @@
         <v>492.63157894736844</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -18690,7 +18643,7 @@
         <v>32.683486238532112</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -18727,7 +18680,7 @@
         <v>46.490566037735846</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -18764,7 +18717,7 @@
         <v>197.31455399061034</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -18801,7 +18754,7 @@
         <v>5.3046875</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -18838,7 +18791,7 @@
         <v>123.83653846153847</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -18875,7 +18828,7 @@
         <v>302.64347826086959</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -18912,7 +18865,7 @@
         <v>1.4602150537634409</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -18949,7 +18902,7 @@
         <v>87.306358381502889</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -18986,7 +18939,7 @@
         <v>117.17105263157895</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -19023,7 +18976,7 @@
         <v>97.875</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -19060,7 +19013,7 @@
         <v>128.76923076923077</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -19097,7 +19050,7 @@
         <v>119.72477064220183</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -19134,7 +19087,7 @@
         <v>127.23809523809524</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -19171,7 +19124,7 @@
         <v>97.125</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -19208,7 +19161,7 @@
         <v>97.033333333333331</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -19245,7 +19198,7 @@
         <v>245.07655502392345</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -19282,7 +19235,7 @@
         <v>285.34848484848487</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -19319,7 +19272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -19356,7 +19309,7 @@
         <v>32.945544554455445</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -19393,7 +19346,7 @@
         <v>124.2279792746114</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -19430,7 +19383,7 @@
         <v>23.289719626168225</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -19467,7 +19420,7 @@
         <v>11.28688524590164</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -19504,7 +19457,7 @@
         <v>141.90173410404626</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -19541,7 +19494,7 @@
         <v>2.2189542483660132</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -19578,7 +19531,7 @@
         <v>274.125</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -19615,7 +19568,7 @@
         <v>68.625</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -19652,7 +19605,7 @@
         <v>78.828828828828833</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -19689,7 +19642,7 @@
         <v>170.99074074074073</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -19726,7 +19679,7 @@
         <v>2.2117263843648209</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -19763,7 +19716,7 @@
         <v>105.63802083333333</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -19800,7 +19753,7 @@
         <v>1.8058510638297873</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -19837,7 +19790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -19874,7 +19827,7 @@
         <v>35.523676880222844</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -19911,7 +19864,7 @@
         <v>53.031446540880502</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -19948,7 +19901,7 @@
         <v>1115.4509803921569</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -19985,7 +19938,7 @@
         <v>2.8771186440677967</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -20022,7 +19975,7 @@
         <v>145.42990654205607</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -20059,7 +20012,7 @@
         <v>300.61627906976742</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -20096,7 +20049,7 @@
         <v>71.561290322580646</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -20133,7 +20086,7 @@
         <v>13.231974921630094</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -20170,7 +20123,7 @@
         <v>508.06451612903226</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -20207,7 +20160,7 @@
         <v>387.82716049382714</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -20244,7 +20197,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -20281,7 +20234,7 @@
         <v>78.432532347504619</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -20318,7 +20271,7 @@
         <v>97.049549549549553</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -20355,7 +20308,7 @@
         <v>97.092979127134726</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -20392,7 +20345,7 @@
         <v>86.325259515570934</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -20429,7 +20382,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>

--- a/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
+++ b/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_01\Excel\Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCACB111-F948-40E4-BDD5-AE46771A3608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0D2DA-322B-4754-A918-FCE24B2B0946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="53">
   <si>
     <t>ProductionID</t>
   </si>
@@ -183,9 +183,6 @@
     <t>Sum of UnitsProduced</t>
   </si>
   <si>
-    <t>2023</t>
-  </si>
-  <si>
     <t>Sep</t>
   </si>
   <si>
@@ -229,6 +226,9 @@
   </si>
   <si>
     <t>Production Dashboard</t>
+  </si>
+  <si>
+    <t>2024</t>
   </si>
 </sst>
 </file>
@@ -314,6 +314,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -326,13 +327,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     </dxf>
@@ -619,19 +634,13 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Automobiles</c:v>
+                  <c:v>Furniture</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Furniture</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -639,21 +648,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>142768</c:v>
+                  <c:v>7125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>679</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>90859</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>178302</c:v>
+                  <c:v>16864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1154,59 +1157,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 2'!$A$4:$A$11</c:f>
+              <c:f>'Pivot 2'!$A$4:$A$5</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jane Smith</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Laura Black</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>David White</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mike Brown</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Nancy Grey</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Andrew Blue</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>John Doe</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 2'!$B$4:$B$11</c:f>
+              <c:f>'Pivot 2'!$B$4:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1651,23 +1618,20 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$7</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Oct</c:v>
+                    <c:v>Feb</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Dec</c:v>
+                    <c:v>Mar</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>2023</c:v>
+                    <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1675,18 +1639,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1143</c:v>
+                  <c:v>318</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1840</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>959</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2187,7 +2148,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFCCCC"/>
+                <a:srgbClr val="FFCC99"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2212,7 +2173,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCFFCC"/>
+                <a:srgbClr val="CCCCFF"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2237,7 +2198,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFCC99"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2262,7 +2223,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2337,19 +2298,13 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Automobiles</c:v>
+                  <c:v>Furniture</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Furniture</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2357,21 +2312,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>116.07783789987161</c:v>
+                  <c:v>32.683486238532112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2117263843648209</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>82.9945217959296</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>178.306304928782</c:v>
+                  <c:v>53.031446540880502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2875,19 +2824,13 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Automobiles</c:v>
+                  <c:v>Furniture</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Furniture</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2895,21 +2838,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>142768</c:v>
+                  <c:v>7125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>679</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>90859</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>178302</c:v>
+                  <c:v>16864</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3576,59 +3513,23 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 2'!$A$4:$A$11</c:f>
+              <c:f>'Pivot 2'!$A$4:$A$5</c:f>
               <c:strCache>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jane Smith</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Laura Black</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>David White</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Mike Brown</c:v>
-                </c:pt>
-                <c:pt idx="4">
                   <c:v>Nancy Grey</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Andrew Blue</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>John Doe</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 2'!$B$4:$B$11</c:f>
+              <c:f>'Pivot 2'!$B$4:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="1">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4211,23 +4112,20 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$7</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Oct</c:v>
+                    <c:v>Feb</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Nov</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Dec</c:v>
+                    <c:v>Mar</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>2023</c:v>
+                    <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -4235,18 +4133,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1143</c:v>
+                  <c:v>318</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1840</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>959</c:v>
+                  <c:v>218</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5021,7 +4916,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFCCCC"/>
+                <a:srgbClr val="FFCC99"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5046,7 +4941,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCFFCC"/>
+                <a:srgbClr val="CCCCFF"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5071,7 +4966,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FFCC99"/>
+                <a:schemeClr val="accent3"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5096,7 +4991,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5171,19 +5066,13 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$6</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Automobiles</c:v>
+                  <c:v>Furniture</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Electronics</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Furniture</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -5191,21 +5080,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>116.07783789987161</c:v>
+                  <c:v>32.683486238532112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.2117263843648209</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>82.9945217959296</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>178.306304928782</c:v>
+                  <c:v>53.031446540880502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13325,7 +13208,7 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A05C44-8E02-4C0B-897E-E209559CB89E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13434,10 +13317,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13455,8 +13338,8 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
       </items>
@@ -13464,9 +13347,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13493,10 +13376,10 @@
     <pivotField showAll="0">
       <items count="7">
         <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
-        <item x="4"/>
+        <item h="1" x="4"/>
         <item h="1" x="5"/>
         <item t="default"/>
       </items>
@@ -13514,13 +13397,7 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="2"/>
     </i>
@@ -13538,7 +13415,7 @@
     <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13576,7 +13453,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE43A99-DA69-49C7-9999-13295477D628}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13685,10 +13562,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13721,8 +13598,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
       </items>
@@ -13730,9 +13607,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13759,10 +13636,10 @@
     <pivotField showAll="0">
       <items count="7">
         <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
-        <item x="4"/>
+        <item h="1" x="4"/>
         <item h="1" x="5"/>
         <item t="default"/>
       </items>
@@ -13780,27 +13657,9 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
+  <rowItems count="2">
     <i>
       <x v="8"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -13846,7 +13705,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D064263-4D1C-40D7-BF76-F231D23CFDA0}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13955,10 +13814,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13968,8 +13827,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
       </items>
@@ -13977,9 +13836,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14006,10 +13865,10 @@
     <pivotField showAll="0">
       <items count="7">
         <item h="1" sd="0" x="0"/>
-        <item h="1" sd="0" x="1"/>
+        <item sd="0" x="1"/>
         <item h="1" sd="0" x="2"/>
         <item h="1" sd="0" x="3"/>
-        <item sd="0" x="4"/>
+        <item h="1" sd="0" x="4"/>
         <item h="1" sd="0" x="5"/>
         <item t="default"/>
       </items>
@@ -14028,18 +13887,15 @@
     <field x="13"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="4">
     <i>
-      <x v="1"/>
+      <x v="2"/>
     </i>
     <i r="1">
-      <x v="10"/>
+      <x v="2"/>
     </i>
     <i r="1">
-      <x v="11"/>
-    </i>
-    <i r="1">
-      <x v="12"/>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -14085,7 +13941,7 @@
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87307F0E-6F33-40F7-A92A-4E423868BB78}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14194,10 +14050,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item x="3"/>
+        <item h="1" x="3"/>
         <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14215,8 +14071,8 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
-        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item t="default"/>
       </items>
@@ -14224,9 +14080,9 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14235,10 +14091,10 @@
     <pivotField showAll="0" defaultSubtotal="0">
       <items count="6">
         <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item h="1" x="2"/>
         <item h="1" x="3"/>
-        <item x="4"/>
+        <item h="1" x="4"/>
         <item h="1" x="5"/>
       </items>
     </pivotField>
@@ -14254,13 +14110,7 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
+  <rowItems count="3">
     <i>
       <x v="2"/>
     </i>
@@ -14569,7 +14419,7 @@
     <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14850,10 +14700,10 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="4">
-        <i x="3" s="1"/>
+        <i x="3"/>
         <i x="2" s="1"/>
-        <i x="0" s="1"/>
-        <i x="1" s="1"/>
+        <i x="0"/>
+        <i x="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -14871,9 +14721,9 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="3">
-        <i x="0" s="1"/>
-        <i x="1"/>
-        <i x="2"/>
+        <i x="1" s="1"/>
+        <i x="0" nd="1"/>
+        <i x="2" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -14891,9 +14741,9 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="3">
-        <i x="0" s="1"/>
+        <i x="0"/>
         <i x="2" s="1"/>
-        <i x="1" s="1"/>
+        <i x="1"/>
       </items>
     </tabular>
   </data>
@@ -14911,10 +14761,10 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="6">
-        <i x="1"/>
+        <i x="1" s="1"/>
         <i x="2"/>
         <i x="3"/>
-        <i x="4" s="1"/>
+        <i x="4"/>
         <i x="0" nd="1"/>
         <i x="5" nd="1"/>
       </items>
@@ -15258,7 +15108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC7590B-59C1-4780-B184-059AA2CBDAFA}">
-  <dimension ref="A3:B8"/>
+  <dimension ref="A3:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15275,42 +15125,26 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5">
-        <v>142768</v>
+        <v>7125</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B5" s="5">
-        <v>679</v>
+        <v>16864</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>90859</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="5">
-        <v>178302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="5">
-        <v>412608</v>
+        <v>23989</v>
       </c>
     </row>
   </sheetData>
@@ -15321,7 +15155,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52287D6-AC2A-495B-8F15-E05B7FBCCBFF}">
-  <dimension ref="A3:B11"/>
+  <dimension ref="A3:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15338,66 +15172,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B4" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B5" s="13">
         <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="13">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -15408,7 +15194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F3A811-0A1A-4FEF-9853-B1FFC57DE7E8}">
-  <dimension ref="A3:B8"/>
+  <dimension ref="A3:B7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15425,42 +15211,34 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B4" s="13">
-        <v>3942</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B5" s="13">
-        <v>1143</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="13">
-        <v>1840</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>41</v>
+      <c r="A7" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="B7" s="13">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="13">
-        <v>3942</v>
+        <v>536</v>
       </c>
     </row>
   </sheetData>
@@ -15472,7 +15250,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31661C08-08AE-40BA-AF39-38EBBD305E22}">
-  <dimension ref="A3:B8"/>
+  <dimension ref="A3:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15484,47 +15262,31 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B4" s="13">
-        <v>116.07783789987161</v>
+        <v>32.683486238532112</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B5" s="13">
-        <v>2.2117263843648209</v>
+        <v>53.031446540880502</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="B6" s="13">
-        <v>82.9945217959296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="13">
-        <v>178.306304928782</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="13">
-        <v>114.04471030444071</v>
+        <v>42.857466389706303</v>
       </c>
     </row>
   </sheetData>
@@ -15539,110 +15301,110 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
+      <c r="A1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="10"/>
+      <c r="V1" s="10"/>
+      <c r="W1" s="10"/>
+      <c r="X1" s="10"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-      <c r="S3" s="9"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="9"/>
-      <c r="W3" s="9"/>
-      <c r="X3" s="9"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15733,70 +15495,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
+      <c r="A1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -15808,7 +15570,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>3026</v>
@@ -15816,7 +15578,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>4127</v>
@@ -15824,7 +15586,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>3875</v>
@@ -15832,7 +15594,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>1528</v>
@@ -15840,7 +15602,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>1684</v>
@@ -15848,7 +15610,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>3537</v>
@@ -15856,7 +15618,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>1536</v>
@@ -15864,7 +15626,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>2864</v>
@@ -15872,7 +15634,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17">
         <v>2150</v>
@@ -15880,7 +15642,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18">
         <v>3103</v>
@@ -15888,7 +15650,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19">
         <v>4803</v>
@@ -15896,7 +15658,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20">
         <v>2494</v>
@@ -15945,37 +15707,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="8" t="s">
         <v>31</v>
       </c>
     </row>

--- a/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
+++ b/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_01\Excel\Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B0D2DA-322B-4754-A918-FCE24B2B0946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62948D3-6880-43A9-AA17-376A8D91C979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot 1" sheetId="8" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="56">
   <si>
     <t>ProductionID</t>
   </si>
@@ -230,6 +230,15 @@
   <si>
     <t>2024</t>
   </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>Product Type</t>
+  </si>
 </sst>
 </file>
 
@@ -332,13 +341,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -634,13 +637,19 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$6</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Automobiles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Furniture</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -648,15 +657,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$6</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7125</c:v>
+                  <c:v>800360</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16864</c:v>
+                  <c:v>341435</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>446302</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>561014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1157,23 +1172,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 2'!$A$4:$A$5</c:f>
+              <c:f>'Pivot 2'!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Nancy Grey</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laura Black</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Andrew Blue</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Mike Brown</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>David White</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sarah Lee</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Chris Green</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 2'!$B$4:$B$5</c:f>
+              <c:f>'Pivot 2'!$B$4:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1618,19 +1687,46 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$16</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="10"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Feb</c:v>
+                    <c:v>Sep</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Mar</c:v>
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>2023</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
                     <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1639,15 +1735,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>318</c:v>
+                  <c:v>771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218</c:v>
+                  <c:v>3103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4803</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2494</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1528</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1684</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3537</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2864</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2013,7 +2133,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="CCCCFF"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -2032,7 +2152,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="FFCCCC"/>
+            <a:srgbClr val="FFCC99"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -2051,7 +2171,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="CCFFCC"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -2070,7 +2190,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="FFCC99"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -2173,7 +2293,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -2298,13 +2418,19 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$6</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Automobiles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Furniture</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2312,15 +2438,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$6</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>32.683486238532112</c:v>
+                  <c:v>136.50595386143647</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.031446540880502</c:v>
+                  <c:v>106.84509125545883</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>157.61176084289789</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>111.05339553555136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2824,13 +2956,19 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 1'!$A$4:$A$6</c:f>
+              <c:f>'Pivot 1'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Automobiles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Furniture</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -2838,15 +2976,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 1'!$B$4:$B$6</c:f>
+              <c:f>'Pivot 1'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>7125</c:v>
+                  <c:v>800360</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16864</c:v>
+                  <c:v>341435</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>446302</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>561014</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3513,23 +3657,77 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 2'!$A$4:$A$5</c:f>
+              <c:f>'Pivot 2'!$A$4:$A$14</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>Nancy Grey</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Jane Smith</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laura Black</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>John Doe</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Andrew Blue</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Mike Brown</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Emily Davis</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>David White</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Sarah Lee</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Chris Green</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 2'!$B$4:$B$5</c:f>
+              <c:f>'Pivot 2'!$B$4:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4112,19 +4310,46 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$7</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$16</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="10"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>Feb</c:v>
+                    <c:v>Sep</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>Mar</c:v>
+                    <c:v>Oct</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Nov</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Dec</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Apr</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>May</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Jun</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Jul</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Aug</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Sep</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
+                    <c:v>2023</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
                     <c:v>2024</c:v>
                   </c:pt>
                 </c:lvl>
@@ -4133,15 +4358,39 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$7</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>318</c:v>
+                  <c:v>771</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>218</c:v>
+                  <c:v>3103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4803</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2494</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1528</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1684</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3537</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2864</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4781,7 +5030,7 @@
         <c:idx val="11"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="FFCCCC"/>
+            <a:srgbClr val="FFCC99"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4800,7 +5049,7 @@
         <c:idx val="12"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="CCFFCC"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4819,7 +5068,7 @@
         <c:idx val="13"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="FFCC99"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4838,7 +5087,7 @@
         <c:idx val="14"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="CCCCFF"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="25400">
             <a:solidFill>
@@ -4941,7 +5190,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="CCCCFF"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="25400">
                 <a:solidFill>
@@ -5066,13 +5315,19 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Pivot 4'!$A$4:$A$6</c:f>
+              <c:f>'Pivot 4'!$A$4:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
+                  <c:v>Automobiles</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Furniture</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Machinery</c:v>
                 </c:pt>
               </c:strCache>
@@ -5080,15 +5335,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 4'!$B$4:$B$6</c:f>
+              <c:f>'Pivot 4'!$B$4:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>32.683486238532112</c:v>
+                  <c:v>136.50595386143647</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>53.031446540880502</c:v>
+                  <c:v>106.84509125545883</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>157.61176084289789</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>111.05339553555136</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10509,16 +10770,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>11430</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -13207,8 +13468,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A05C44-8E02-4C0B-897E-E209559CB89E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
-  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B4A05C44-8E02-4C0B-897E-E209559CB89E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Product Type">
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13317,10 +13578,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="2"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13338,18 +13599,18 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13375,12 +13636,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13397,7 +13658,13 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
@@ -13412,10 +13679,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Total Cost" fld="6" baseField="4" baseItem="2" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="6">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13453,7 +13720,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4EE43A99-DA69-49C7-9999-13295477D628}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13562,10 +13829,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="2"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13598,18 +13865,18 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13635,12 +13902,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13657,9 +13924,36 @@
   <rowFields count="1">
     <field x="3"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="11">
     <i>
       <x v="8"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -13705,7 +13999,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D064263-4D1C-40D7-BF76-F231D23CFDA0}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -13814,10 +14108,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="2"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13827,18 +14121,18 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13864,12 +14158,12 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="7">
-        <item h="1" sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item h="1" sd="0" x="2"/>
-        <item h="1" sd="0" x="3"/>
-        <item h="1" sd="0" x="4"/>
-        <item h="1" sd="0" x="5"/>
+        <item sd="0" x="0"/>
+        <item h="1" sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13887,15 +14181,42 @@
     <field x="13"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="13">
+    <i>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="1">
+      <x v="10"/>
+    </i>
+    <i r="1">
+      <x v="11"/>
+    </i>
+    <i r="1">
+      <x v="12"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
     <i r="1">
-      <x v="2"/>
+      <x v="4"/>
     </i>
     <i r="1">
-      <x v="3"/>
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
     </i>
     <i t="grand">
       <x/>
@@ -13941,7 +14262,7 @@
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87307F0E-6F33-40F7-A92A-4E423868BB78}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14050,10 +14371,10 @@
     </pivotField>
     <pivotField showAll="0">
       <items count="5">
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item x="2"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
+        <item x="0"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14071,18 +14392,18 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="1"/>
-        <item h="1" x="2"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="2"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -14090,12 +14411,12 @@
     <pivotField showAll="0" defaultSubtotal="0"/>
     <pivotField showAll="0" defaultSubtotal="0">
       <items count="6">
-        <item h="1" x="0"/>
-        <item x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
       </items>
     </pivotField>
     <pivotField showAll="0" defaultSubtotal="0">
@@ -14110,7 +14431,13 @@
   <rowFields count="1">
     <field x="4"/>
   </rowFields>
-  <rowItems count="3">
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
     <i>
       <x v="2"/>
     </i>
@@ -14419,7 +14746,7 @@
     <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="5">
+    <format dxfId="3">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -14700,10 +15027,10 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="4">
-        <i x="3"/>
+        <i x="3" s="1"/>
         <i x="2" s="1"/>
-        <i x="0"/>
-        <i x="1" nd="1"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -14721,9 +15048,9 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="3">
+        <i x="0" s="1"/>
         <i x="1" s="1"/>
-        <i x="0" nd="1"/>
-        <i x="2" nd="1"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -14741,9 +15068,9 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="3">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="2" s="1"/>
-        <i x="1"/>
+        <i x="1" s="1"/>
       </items>
     </tabular>
   </data>
@@ -14761,12 +15088,12 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="6">
-        <i x="1" s="1"/>
-        <i x="2"/>
-        <i x="3"/>
-        <i x="4"/>
-        <i x="0" nd="1"/>
-        <i x="5" nd="1"/>
+        <i x="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="0" s="1" nd="1"/>
+        <i x="5" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -14833,7 +15160,7 @@
   <slicer name="Region" xr10:uid="{9190ECA8-014F-4A4A-BEEC-CF300AC8D463}" cache="Slicer_Region" caption="Region" rowHeight="234950"/>
   <slicer name="Gender" xr10:uid="{BD07F61C-21A6-48A3-964E-72CBA6063C43}" cache="Slicer_Gender" caption="Gender" rowHeight="234950"/>
   <slicer name="Age Groups" xr10:uid="{8AFE9850-E87D-41A3-B551-3DF3ED874B5D}" cache="Slicer_Age_Groups" caption="Age Groups" rowHeight="234950"/>
-  <slicer name="Quarters (ProductionDate)" xr10:uid="{6323FAC9-8D51-47DE-8A27-A0AAC300EABF}" cache="Slicer_Quarters__ProductionDate" caption="Quarters (ProductionDate)" rowHeight="234950"/>
+  <slicer name="Quarters (ProductionDate)" xr10:uid="{6323FAC9-8D51-47DE-8A27-A0AAC300EABF}" cache="Slicer_Quarters__ProductionDate" caption="Quarters (ProductionDate)" startItem="1" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -15108,43 +15435,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBC7590B-59C1-4780-B184-059AA2CBDAFA}">
-  <dimension ref="A3:B6"/>
+  <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5">
-        <v>7125</v>
+        <v>800360</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B5" s="5">
-        <v>16864</v>
+        <v>341435</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="5">
+        <v>446302</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5">
+        <v>561014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="5">
-        <v>23989</v>
+      <c r="B8" s="5">
+        <v>2149111</v>
       </c>
     </row>
   </sheetData>
@@ -15155,7 +15498,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F52287D6-AC2A-495B-8F15-E05B7FBCCBFF}">
-  <dimension ref="A3:B5"/>
+  <dimension ref="A3:B14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15175,15 +15518,87 @@
         <v>24</v>
       </c>
       <c r="B4" s="13">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="13">
-        <v>2</v>
+      <c r="B14" s="13">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -15194,7 +15609,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F3A811-0A1A-4FEF-9853-B1FFC57DE7E8}">
-  <dimension ref="A3:B7"/>
+  <dimension ref="A3:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15211,34 +15626,106 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="13">
-        <v>536</v>
+        <v>11171</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B5" s="13">
-        <v>318</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="13">
-        <v>218</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="13">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="13">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" s="13">
+        <v>12528</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="13">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="13">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="13">
+        <v>3537</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="13">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="13">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="13">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="13">
-        <v>536</v>
+      <c r="B16" s="13">
+        <v>23699</v>
       </c>
     </row>
   </sheetData>
@@ -15250,7 +15737,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31661C08-08AE-40BA-AF39-38EBBD305E22}">
-  <dimension ref="A3:B6"/>
+  <dimension ref="A3:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15267,26 +15754,42 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" s="13">
-        <v>32.683486238532112</v>
+        <v>136.50595386143647</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B5" s="13">
-        <v>53.031446540880502</v>
+        <v>106.84509125545883</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="13">
+        <v>157.61176084289789</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="13">
+        <v>111.05339553555136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="13">
-        <v>42.857466389706303</v>
+      <c r="B8" s="13">
+        <v>128.2240455479031</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
+++ b/Excel/Dynamic_Dashboard/Excel+Dashboard+2 (4).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_01\Excel\Dynamic_Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62948D3-6880-43A9-AA17-376A8D91C979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75248ECE-9646-4786-A008-6A073495ADB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot 1" sheetId="8" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="56">
   <si>
     <t>ProductionID</t>
   </si>
@@ -341,7 +341,34 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -662,16 +689,16 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>800360</c:v>
+                  <c:v>1152805</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341435</c:v>
+                  <c:v>604575</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>446302</c:v>
+                  <c:v>703282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561014</c:v>
+                  <c:v>910416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1182,28 +1209,28 @@
                   <c:v>Jane Smith</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Laura Black</c:v>
+                  <c:v>John Doe</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>John Doe</c:v>
+                  <c:v>Mike Brown</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Andrew Blue</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Mike Brown</c:v>
+                  <c:v>Laura Black</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Emily Davis</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Chris Green</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>David White</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Sarah Lee</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Chris Green</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1215,34 +1242,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>26</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1687,9 +1714,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$16</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$19</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Sep</c:v>
@@ -1704,21 +1731,30 @@
                     <c:v>Dec</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
                     <c:v>Apr</c:v>
                   </c:pt>
-                  <c:pt idx="5">
+                  <c:pt idx="8">
                     <c:v>May</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="9">
                     <c:v>Jun</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="10">
                     <c:v>Jul</c:v>
                   </c:pt>
-                  <c:pt idx="8">
+                  <c:pt idx="11">
                     <c:v>Aug</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="12">
                     <c:v>Sep</c:v>
                   </c:pt>
                 </c:lvl>
@@ -1735,10 +1771,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$16</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>771</c:v>
                 </c:pt>
@@ -1752,21 +1788,30 @@
                   <c:v>2494</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>3026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4127</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3875</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1528</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>1684</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>3537</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>1536</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2864</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
@@ -2443,16 +2488,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>136.50595386143647</c:v>
+                  <c:v>140.87387695413258</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106.84509125545883</c:v>
+                  <c:v>108.368246516667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>157.61176084289789</c:v>
+                  <c:v>180.4410334877862</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>111.05339553555136</c:v>
+                  <c:v>108.97659894637712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2981,16 +3026,16 @@
                 <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>800360</c:v>
+                  <c:v>1152805</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>341435</c:v>
+                  <c:v>604575</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>446302</c:v>
+                  <c:v>703282</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>561014</c:v>
+                  <c:v>910416</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3667,28 +3712,28 @@
                   <c:v>Jane Smith</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Laura Black</c:v>
+                  <c:v>John Doe</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>John Doe</c:v>
+                  <c:v>Mike Brown</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Andrew Blue</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Mike Brown</c:v>
+                  <c:v>Laura Black</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Emily Davis</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>Chris Green</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>David White</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Sarah Lee</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Chris Green</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3700,34 +3745,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>26</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12</c:v>
+                  <c:v>18</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>4</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4310,9 +4355,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Pivot 3'!$A$4:$A$16</c:f>
+              <c:f>'Pivot 3'!$A$4:$A$19</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>Sep</c:v>
@@ -4327,21 +4372,30 @@
                     <c:v>Dec</c:v>
                   </c:pt>
                   <c:pt idx="4">
+                    <c:v>Jan</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>Feb</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Mar</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
                     <c:v>Apr</c:v>
                   </c:pt>
-                  <c:pt idx="5">
+                  <c:pt idx="8">
                     <c:v>May</c:v>
                   </c:pt>
-                  <c:pt idx="6">
+                  <c:pt idx="9">
                     <c:v>Jun</c:v>
                   </c:pt>
-                  <c:pt idx="7">
+                  <c:pt idx="10">
                     <c:v>Jul</c:v>
                   </c:pt>
-                  <c:pt idx="8">
+                  <c:pt idx="11">
                     <c:v>Aug</c:v>
                   </c:pt>
-                  <c:pt idx="9">
+                  <c:pt idx="12">
                     <c:v>Sep</c:v>
                   </c:pt>
                 </c:lvl>
@@ -4358,10 +4412,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Pivot 3'!$B$4:$B$16</c:f>
+              <c:f>'Pivot 3'!$B$4:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="13"/>
                 <c:pt idx="0">
                   <c:v>771</c:v>
                 </c:pt>
@@ -4375,21 +4429,30 @@
                   <c:v>2494</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>3026</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4127</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3875</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>1528</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>1684</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>3537</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>1536</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>2864</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>1379</c:v>
                 </c:pt>
               </c:numCache>
@@ -5340,16 +5403,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>136.50595386143647</c:v>
+                  <c:v>140.87387695413258</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>106.84509125545883</c:v>
+                  <c:v>108.368246516667</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>157.61176084289789</c:v>
+                  <c:v>180.4410334877862</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>111.05339553555136</c:v>
+                  <c:v>108.97659894637712</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13637,7 +13700,7 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
@@ -13682,7 +13745,7 @@
     <dataField name="Total Cost" fld="6" baseField="4" baseItem="2" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="4">
+    <format dxfId="13">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -13903,7 +13966,7 @@
     <pivotField showAll="0">
       <items count="7">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
@@ -13932,28 +13995,28 @@
       <x v="4"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="7"/>
     </i>
     <i>
       <x/>
     </i>
     <i>
-      <x v="7"/>
+      <x v="6"/>
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i>
+      <x v="1"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
       <x v="9"/>
-    </i>
-    <i>
-      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -13999,7 +14062,7 @@
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8D064263-4D1C-40D7-BF76-F231D23CFDA0}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
-  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -14159,7 +14222,7 @@
     <pivotField showAll="0">
       <items count="7">
         <item sd="0" x="0"/>
-        <item h="1" sd="0" x="1"/>
+        <item sd="0" x="1"/>
         <item sd="0" x="2"/>
         <item sd="0" x="3"/>
         <item sd="0" x="4"/>
@@ -14181,7 +14244,7 @@
     <field x="13"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="16">
     <i>
       <x v="1"/>
     </i>
@@ -14199,6 +14262,15 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
     </i>
     <i r="1">
       <x v="4"/>
@@ -14412,7 +14484,7 @@
     <pivotField showAll="0" defaultSubtotal="0">
       <items count="6">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
@@ -14746,7 +14818,7 @@
     <dataField name="Sum of TotalCost" fld="6" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="3">
+    <format dxfId="12">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -15088,7 +15160,7 @@
   <data>
     <tabular pivotCacheId="984892114">
       <items count="6">
-        <i x="1"/>
+        <i x="1" s="1"/>
         <i x="2" s="1"/>
         <i x="3" s="1"/>
         <i x="4" s="1"/>
@@ -15455,7 +15527,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="5">
-        <v>800360</v>
+        <v>1152805</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15463,7 +15535,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="5">
-        <v>341435</v>
+        <v>604575</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15471,7 +15543,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="5">
-        <v>446302</v>
+        <v>703282</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15479,7 +15551,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="5">
-        <v>561014</v>
+        <v>910416</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15487,7 +15559,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="5">
-        <v>2149111</v>
+        <v>3371078</v>
       </c>
     </row>
   </sheetData>
@@ -15518,7 +15590,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="13">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15526,23 +15598,23 @@
         <v>20</v>
       </c>
       <c r="B5" s="13">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="13">
         <v>13</v>
-      </c>
-      <c r="B6" s="13">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B7" s="13">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15550,15 +15622,15 @@
         <v>21</v>
       </c>
       <c r="B8" s="13">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B9" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -15566,31 +15638,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B11" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B12" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B13" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -15598,7 +15670,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="13">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -15609,7 +15681,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F3A811-0A1A-4FEF-9853-B1FFC57DE7E8}">
-  <dimension ref="A3:B16"/>
+  <dimension ref="A3:B19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -15669,63 +15741,87 @@
         <v>52</v>
       </c>
       <c r="B9" s="13">
-        <v>12528</v>
+        <v>23556</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" s="13">
-        <v>1528</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" s="13">
-        <v>1684</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B12" s="13">
-        <v>3537</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B13" s="13">
-        <v>1536</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B14" s="13">
-        <v>2864</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B15" s="13">
-        <v>1379</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="13">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="13">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="13">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B16" s="13">
-        <v>23699</v>
+      <c r="B19" s="13">
+        <v>34727</v>
       </c>
     </row>
   </sheetData>
@@ -15757,7 +15853,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="13">
-        <v>136.50595386143647</v>
+        <v>140.87387695413258</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -15765,7 +15861,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="13">
-        <v>106.84509125545883</v>
+        <v>108.368246516667</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -15773,7 +15869,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="13">
-        <v>157.61176084289789</v>
+        <v>180.4410334877862</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -15781,7 +15877,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="13">
-        <v>111.05339553555136</v>
+        <v>108.97659894637712</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -15789,7 +15885,7 @@
         <v>33</v>
       </c>
       <c r="B8" s="13">
-        <v>128.2240455479031</v>
+        <v>132.39235089555021</v>
       </c>
     </row>
   </sheetData>
